--- a/Planification/Organisation mini-projet(Feuil1).xlsx
+++ b/Planification/Organisation mini-projet(Feuil1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elric.evrard\Documents\GitHub\SovLink\Planification\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{127768A1-8F69-41AB-8F78-6D8A82E4738E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19AB3B7E-14B1-4A5E-BCA8-E8FD7ECD058D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{026A8FE1-52B5-40A2-BA56-3AC0082A12E1}"/>
   </bookViews>
@@ -40,7 +40,7 @@
     <t>2h fin du cahier des charge et readme</t>
   </si>
   <si>
-    <t>3h configuration du serveur, 1h développement de clé publique / clé privée lors du lancement du client</t>
+    <t>1h debug du programme côter client, 2h développement de clé publique / clé privée lors du lancement du client, 1h commencer la suppression automatique des messages après 30s</t>
   </si>
 </sst>
 </file>
@@ -942,7 +942,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="116.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="216" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>46108</v>
       </c>

--- a/Planification/Organisation mini-projet(Feuil1).xlsx
+++ b/Planification/Organisation mini-projet(Feuil1).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elric.evrard\Documents\GitHub\SovLink\Planification\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19AB3B7E-14B1-4A5E-BCA8-E8FD7ECD058D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B26551A-7D91-4B83-B2F5-7A97B1BC99BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{026A8FE1-52B5-40A2-BA56-3AC0082A12E1}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>dates</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t>1h debug du programme côter client, 2h développement de clé publique / clé privée lors du lancement du client, 1h commencer la suppression automatique des messages après 30s</t>
+  </si>
+  <si>
+    <t>2h Debugage du client (problème de library) 2h developpement de la suppression auto de messages</t>
+  </si>
+  <si>
+    <t>2h dev sur la génération des clés privées clés publiques 2h debug serveur</t>
   </si>
 </sst>
 </file>
@@ -524,7 +530,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -534,6 +540,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -910,7 +922,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00DF7F4C-18C0-4C55-814B-981838154A60}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.7109375" customWidth="1"/>
@@ -950,6 +962,17 @@
         <v>6</v>
       </c>
     </row>
+    <row r="4" spans="1:4" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>46111</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
